--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.5524865872714</v>
+        <v>1.552279070431603</v>
       </c>
       <c r="D2" t="n">
-        <v>7.613129706212233</v>
+        <v>1.237133577259488</v>
       </c>
       <c r="E2" t="n">
-        <v>15.54059151763463</v>
+        <v>2.525346121615628</v>
       </c>
       <c r="F2" t="n">
-        <v>15.28155209616778</v>
+        <v>2.483252215627265</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.641347287825317</v>
+        <v>1.404218934271614</v>
       </c>
       <c r="D3" t="n">
-        <v>10.61903199080417</v>
+        <v>1.725592698505678</v>
       </c>
       <c r="E3" t="n">
-        <v>15.54059151763463</v>
+        <v>2.525346121615628</v>
       </c>
       <c r="F3" t="n">
-        <v>15.28155209616778</v>
+        <v>2.483252215627265</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.11265012134343</v>
+        <v>6.680805644718308</v>
       </c>
       <c r="D4" t="n">
-        <v>39.14584580672145</v>
+        <v>6.361199943592236</v>
       </c>
       <c r="E4" t="n">
-        <v>15.54059151763463</v>
+        <v>2.525346121615628</v>
       </c>
       <c r="F4" t="n">
-        <v>15.28155209616778</v>
+        <v>2.483252215627265</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.15733710734282</v>
+        <v>4.738067279943207</v>
       </c>
       <c r="D5" t="n">
-        <v>31.19369713135762</v>
+        <v>5.068975783845612</v>
       </c>
       <c r="E5" t="n">
-        <v>15.54059151763463</v>
+        <v>2.525346121615628</v>
       </c>
       <c r="F5" t="n">
-        <v>15.28155209616778</v>
+        <v>2.483252215627265</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.541979105689229</v>
+        <v>1.2255716046745</v>
       </c>
       <c r="D6" t="n">
-        <v>7.033806166821215</v>
+        <v>1.142993502108447</v>
       </c>
       <c r="E6" t="n">
-        <v>15.54059151763463</v>
+        <v>2.525346121615628</v>
       </c>
       <c r="F6" t="n">
-        <v>15.28155209616778</v>
+        <v>2.483252215627265</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.45384592454143</v>
+        <v>6.898749962737983</v>
       </c>
       <c r="D7" t="n">
-        <v>41.89091825539416</v>
+        <v>6.807274216501551</v>
       </c>
       <c r="E7" t="n">
-        <v>15.54059151763463</v>
+        <v>2.525346121615628</v>
       </c>
       <c r="F7" t="n">
-        <v>15.28155209616778</v>
+        <v>2.483252215627265</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.4049378636541</v>
+        <v>6.890802402843791</v>
       </c>
       <c r="D8" t="n">
-        <v>41.78171347130195</v>
+        <v>6.789528439086567</v>
       </c>
       <c r="E8" t="n">
-        <v>15.54059151763463</v>
+        <v>2.525346121615628</v>
       </c>
       <c r="F8" t="n">
-        <v>15.28155209616778</v>
+        <v>2.483252215627265</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
